--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,21 @@
   </si>
   <si>
     <t>Resting and learning skills.</t>
+  </si>
+  <si>
+    <t>Relaxing and coding.</t>
+  </si>
+  <si>
+    <t>Coding and learning skills.</t>
+  </si>
+  <si>
+    <t>Tired and complete the tasks.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Do the tasks related to the classes.</t>
   </si>
 </sst>
 </file>
@@ -1522,8 +1537,8 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.57407407407407" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.287037037037" customWidth="1"/>
-    <col min="2" max="2" width="11" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="10.8888888888889" customWidth="1"/>
     <col min="3" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
@@ -1698,7 +1713,9 @@
       <c r="A7" s="8">
         <v>46247</v>
       </c>
-      <c r="B7" s="9"/>
+      <c r="B7" s="9">
+        <v>360</v>
+      </c>
       <c r="C7" s="9">
         <v>60</v>
       </c>
@@ -1719,11 +1736,11 @@
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>1180</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>260</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>56</v>
@@ -1742,7 +1759,9 @@
       <c r="A8" s="8">
         <v>46248</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="9">
+        <v>420</v>
+      </c>
       <c r="C8" s="9">
         <v>60</v>
       </c>
@@ -1763,11 +1782,11 @@
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>865</v>
+        <v>1285</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="1"/>
-        <v>575</v>
+        <v>155</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>56</v>
@@ -1786,7 +1805,9 @@
       <c r="A9" s="8">
         <v>46249</v>
       </c>
-      <c r="B9" s="9"/>
+      <c r="B9" s="9">
+        <v>480</v>
+      </c>
       <c r="C9" s="9">
         <v>60</v>
       </c>
@@ -1807,11 +1828,11 @@
       </c>
       <c r="I9" s="13">
         <f t="shared" si="0"/>
-        <v>510</v>
+        <v>990</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>450</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>52</v>
@@ -1830,7 +1851,9 @@
       <c r="A10" s="8">
         <v>46250</v>
       </c>
-      <c r="B10" s="9"/>
+      <c r="B10" s="9">
+        <v>480</v>
+      </c>
       <c r="C10" s="9">
         <v>60</v>
       </c>
@@ -1851,11 +1874,11 @@
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="1"/>
-        <v>920</v>
+        <v>440</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>57</v>
@@ -1874,7 +1897,9 @@
       <c r="A11" s="8">
         <v>46251</v>
       </c>
-      <c r="B11" s="9"/>
+      <c r="B11" s="9">
+        <v>480</v>
+      </c>
       <c r="C11" s="9">
         <v>60</v>
       </c>
@@ -1895,11 +1920,11 @@
       </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>565</v>
+        <v>1045</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="1"/>
-        <v>875</v>
+        <v>395</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>62</v>
@@ -1918,7 +1943,9 @@
       <c r="A12" s="8">
         <v>46252</v>
       </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="9">
+        <v>420</v>
+      </c>
       <c r="C12" s="9">
         <v>60</v>
       </c>
@@ -1939,11 +1966,11 @@
       </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>1240</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>200</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>57</v>
@@ -1962,7 +1989,9 @@
       <c r="A13" s="8">
         <v>46253</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="9">
+        <v>420</v>
+      </c>
       <c r="C13" s="9">
         <v>60</v>
       </c>
@@ -1983,11 +2012,11 @@
       </c>
       <c r="I13" s="13">
         <f t="shared" si="0"/>
-        <v>650</v>
+        <v>1070</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v>790</v>
+        <v>370</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>57</v>
@@ -2006,7 +2035,9 @@
       <c r="A14" s="8">
         <v>46254</v>
       </c>
-      <c r="B14" s="9"/>
+      <c r="B14" s="9">
+        <v>480</v>
+      </c>
       <c r="C14" s="9">
         <v>60</v>
       </c>
@@ -2027,11 +2058,11 @@
       </c>
       <c r="I14" s="13">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>1340</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>57</v>
@@ -2050,7 +2081,9 @@
       <c r="A15" s="8">
         <v>46255</v>
       </c>
-      <c r="B15" s="9"/>
+      <c r="B15" s="9">
+        <v>300</v>
+      </c>
       <c r="C15" s="9">
         <v>60</v>
       </c>
@@ -2071,11 +2104,11 @@
       </c>
       <c r="I15" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1220</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>220</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>57</v>
@@ -2094,7 +2127,9 @@
       <c r="A16" s="8">
         <v>46256</v>
       </c>
-      <c r="B16" s="9"/>
+      <c r="B16" s="9">
+        <v>300</v>
+      </c>
       <c r="C16" s="9">
         <v>0</v>
       </c>
@@ -2115,11 +2150,11 @@
       </c>
       <c r="I16" s="13">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="J16" s="13">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>540</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>52</v>
@@ -2135,92 +2170,188 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="13" t="str">
+      <c r="A17" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="9">
+        <v>480</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>120</v>
+      </c>
+      <c r="E17" s="9">
+        <v>120</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>240</v>
+      </c>
+      <c r="I17" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J17" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="13" t="str">
+      <c r="A18" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="9">
+        <v>300</v>
+      </c>
+      <c r="C18" s="9">
+        <v>60</v>
+      </c>
+      <c r="D18" s="9">
+        <v>120</v>
+      </c>
+      <c r="E18" s="9">
+        <v>120</v>
+      </c>
+      <c r="F18" s="9">
+        <v>150</v>
+      </c>
+      <c r="G18" s="9">
+        <v>3</v>
+      </c>
+      <c r="H18" s="9">
+        <v>120</v>
+      </c>
+      <c r="I18" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="13" t="str">
+        <v>870</v>
+      </c>
+      <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="13" t="str">
+      <c r="A19" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="9">
+        <v>420</v>
+      </c>
+      <c r="C19" s="9">
+        <v>60</v>
+      </c>
+      <c r="D19" s="9">
+        <v>120</v>
+      </c>
+      <c r="E19" s="9">
+        <v>60</v>
+      </c>
+      <c r="F19" s="9">
+        <v>350</v>
+      </c>
+      <c r="G19" s="9">
+        <v>7</v>
+      </c>
+      <c r="H19" s="9">
+        <v>180</v>
+      </c>
+      <c r="I19" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="13" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="13" t="str">
+        <v>250</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:14">
+      <c r="A20" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="9">
+        <v>480</v>
+      </c>
+      <c r="C20" s="9">
+        <v>60</v>
+      </c>
+      <c r="D20" s="9">
+        <v>180</v>
+      </c>
+      <c r="E20" s="9">
+        <v>180</v>
+      </c>
+      <c r="F20" s="9">
+        <v>200</v>
+      </c>
+      <c r="G20" s="9">
+        <v>4</v>
+      </c>
+      <c r="H20" s="9">
+        <v>180</v>
+      </c>
+      <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="13" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J20" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="16"/>
+        <v>160</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8280" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -249,10 +249,10 @@
     <t>Tired and complete the tasks.</t>
   </si>
   <si>
-    <t>Excellent</t>
+    <t>Do the tasks related to the classes.</t>
   </si>
   <si>
-    <t>Do the tasks related to the classes.</t>
+    <t>Sleepy and felt a bit tired.</t>
   </si>
 </sst>
 </file>
@@ -2341,7 +2341,7 @@
         <v>160</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="L20" s="14" t="s">
         <v>53</v>
@@ -2350,30 +2350,54 @@
         <v>54</v>
       </c>
       <c r="N20" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="9">
+        <v>420</v>
+      </c>
+      <c r="C21" s="9">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9">
+        <v>120</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>350</v>
+      </c>
+      <c r="G21" s="9">
+        <v>7</v>
+      </c>
+      <c r="H21" s="9">
+        <v>60</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="16" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="16"/>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Sleepy and felt a bit tired.</t>
+  </si>
+  <si>
+    <t>Enjoy the rakhi festival and feels like heavy because I was away from the home.</t>
   </si>
 </sst>
 </file>
@@ -2399,27 +2402,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="13" t="str">
+    <row r="22" ht="43.2" spans="1:14">
+      <c r="A22" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="9">
+        <v>540</v>
+      </c>
+      <c r="C22" s="9">
+        <v>60</v>
+      </c>
+      <c r="D22" s="9">
+        <v>30</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>300</v>
+      </c>
+      <c r="G22" s="9">
+        <v>6</v>
+      </c>
+      <c r="H22" s="9">
+        <v>120</v>
+      </c>
+      <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="13" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,7 +255,13 @@
     <t>Sleepy and felt a bit tired.</t>
   </si>
   <si>
-    <t>Enjoy the rakhi festival and feels like heavy because I was away from the home.</t>
+    <t>Enjoy the rakhi festival and feels heavy because I was away from the home.</t>
+  </si>
+  <si>
+    <t>Preperation for CA and Coding.</t>
+  </si>
+  <si>
+    <t>Preperation for the CA.</t>
   </si>
 </sst>
 </file>
@@ -2449,70 +2455,142 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="13" t="str">
+      <c r="A23" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="9">
+        <v>480</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>60</v>
+      </c>
+      <c r="E23" s="9">
+        <v>120</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>120</v>
+      </c>
+      <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="13" t="str">
+        <v>780</v>
+      </c>
+      <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="13" t="str">
+      <c r="A24" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="9">
+        <v>420</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>180</v>
+      </c>
+      <c r="E24" s="9">
+        <v>60</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>180</v>
+      </c>
+      <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="13" t="str">
+        <v>840</v>
+      </c>
+      <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="13" t="str">
+      <c r="A25" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="9">
+        <v>540</v>
+      </c>
+      <c r="C25" s="9">
+        <v>60</v>
+      </c>
+      <c r="D25" s="9">
+        <v>120</v>
+      </c>
+      <c r="E25" s="9">
+        <v>30</v>
+      </c>
+      <c r="F25" s="9">
+        <v>350</v>
+      </c>
+      <c r="G25" s="9">
+        <v>7</v>
+      </c>
+      <c r="H25" s="9">
+        <v>180</v>
+      </c>
+      <c r="I25" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="13" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J25" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="16"/>
+        <v>160</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Preperation for the CA.</t>
+  </si>
+  <si>
+    <t>Work on Analytical Skills.</t>
   </si>
 </sst>
 </file>
@@ -2593,26 +2596,50 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="13" t="str">
+      <c r="A26" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="9">
+        <v>540</v>
+      </c>
+      <c r="C26" s="9">
+        <v>60</v>
+      </c>
+      <c r="D26" s="9">
+        <v>300</v>
+      </c>
+      <c r="E26" s="9">
+        <v>30</v>
+      </c>
+      <c r="F26" s="9">
+        <v>200</v>
+      </c>
+      <c r="G26" s="9">
+        <v>4</v>
+      </c>
+      <c r="H26" s="9">
+        <v>120</v>
+      </c>
+      <c r="I26" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="13" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J26" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Work on Analytical Skills.</t>
+  </si>
+  <si>
+    <t>CA of Communication Skills be Completed.</t>
   </si>
 </sst>
 </file>
@@ -2641,27 +2644,51 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="13" t="str">
+    <row r="27" ht="28.8" spans="1:14">
+      <c r="A27" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="9">
+        <v>480</v>
+      </c>
+      <c r="C27" s="9">
+        <v>60</v>
+      </c>
+      <c r="D27" s="9">
+        <v>180</v>
+      </c>
+      <c r="E27" s="9">
+        <v>30</v>
+      </c>
+      <c r="F27" s="9">
+        <v>350</v>
+      </c>
+      <c r="G27" s="9">
+        <v>7</v>
+      </c>
+      <c r="H27" s="9">
+        <v>120</v>
+      </c>
+      <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="13" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J27" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>CA of Communication Skills be Completed.</t>
+  </si>
+  <si>
+    <t>Prepare for the CA.</t>
   </si>
 </sst>
 </file>
@@ -2691,26 +2694,50 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="13" t="str">
+      <c r="A28" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="9">
+        <v>420</v>
+      </c>
+      <c r="C28" s="9">
+        <v>60</v>
+      </c>
+      <c r="D28" s="9">
+        <v>180</v>
+      </c>
+      <c r="E28" s="9">
+        <v>30</v>
+      </c>
+      <c r="F28" s="9">
+        <v>300</v>
+      </c>
+      <c r="G28" s="9">
+        <v>6</v>
+      </c>
+      <c r="H28" s="9">
+        <v>120</v>
+      </c>
+      <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="13" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2740,26 +2740,50 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="13" t="str">
+      <c r="A29" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="9">
+        <v>120</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>240</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>120</v>
+      </c>
+      <c r="I29" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="13" t="str">
+        <v>480</v>
+      </c>
+      <c r="J29" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="16"/>
+        <v>960</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Prepare for the CA.</t>
+  </si>
+  <si>
+    <t>Prepare for the CA</t>
   </si>
 </sst>
 </file>
@@ -2786,26 +2789,50 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="13" t="str">
+      <c r="A30" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="9">
+        <v>360</v>
+      </c>
+      <c r="C30" s="9">
+        <v>60</v>
+      </c>
+      <c r="D30" s="9">
+        <v>120</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>150</v>
+      </c>
+      <c r="G30" s="9">
+        <v>3</v>
+      </c>
+      <c r="H30" s="9">
+        <v>120</v>
+      </c>
+      <c r="I30" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="13" t="str">
+        <v>810</v>
+      </c>
+      <c r="J30" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8280" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,10 +270,10 @@
     <t>CA of Communication Skills be Completed.</t>
   </si>
   <si>
-    <t>Prepare for the CA.</t>
+    <t>Learning Skills and do the tasks which are given by faculty.</t>
   </si>
   <si>
-    <t>Prepare for the CA</t>
+    <t>Felt tired.</t>
   </si>
 </sst>
 </file>
@@ -2739,7 +2739,7 @@
         <v>54</v>
       </c>
       <c r="N28" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2785,7 +2785,7 @@
         <v>54</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2831,52 +2831,100 @@
         <v>59</v>
       </c>
       <c r="N30" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" ht="28.8" spans="1:14">
+      <c r="A31" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="9">
+        <v>360</v>
+      </c>
+      <c r="C31" s="9">
+        <v>60</v>
+      </c>
+      <c r="D31" s="9">
+        <v>240</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>200</v>
+      </c>
+      <c r="G31" s="9">
+        <v>4</v>
+      </c>
+      <c r="H31" s="9">
+        <v>180</v>
+      </c>
+      <c r="I31" s="13">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J31" s="13">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="9">
+        <v>300</v>
+      </c>
+      <c r="C32" s="9">
+        <v>60</v>
+      </c>
+      <c r="D32" s="9">
+        <v>180</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>350</v>
+      </c>
+      <c r="G32" s="9">
+        <v>7</v>
+      </c>
+      <c r="H32" s="9">
+        <v>180</v>
+      </c>
+      <c r="I32" s="13">
+        <f t="shared" si="0"/>
+        <v>1070</v>
+      </c>
+      <c r="J32" s="13">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="16" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="16"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="16"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Felt tired.</t>
+  </si>
+  <si>
+    <t>Little bit felt low.</t>
   </si>
 </sst>
 </file>
@@ -2927,26 +2930,50 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="13" t="str">
+      <c r="A33" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="9">
+        <v>120</v>
+      </c>
+      <c r="C33" s="9">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9">
+        <v>120</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9">
+        <v>200</v>
+      </c>
+      <c r="G33" s="9">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9">
+        <v>180</v>
+      </c>
+      <c r="I33" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="13" t="str">
+        <v>680</v>
+      </c>
+      <c r="J33" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="16"/>
+        <v>760</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="8"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Little bit felt low.</t>
+  </si>
+  <si>
+    <t>Tired.</t>
   </si>
 </sst>
 </file>
@@ -2933,11 +2936,11 @@
       <c r="A33" s="8">
         <v>46274</v>
       </c>
-      <c r="B33" s="9">
-        <v>120</v>
-      </c>
-      <c r="C33" s="9">
-        <v>60</v>
+      <c r="B33" s="8">
+        <v>46275</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46276</v>
       </c>
       <c r="D33" s="9">
         <v>120</v>
@@ -2956,11 +2959,11 @@
       </c>
       <c r="I33" s="13">
         <f t="shared" si="0"/>
-        <v>680</v>
+        <v>93051</v>
       </c>
       <c r="J33" s="13">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>-91611</v>
       </c>
       <c r="K33" s="14" t="s">
         <v>57</v>
@@ -2976,48 +2979,96 @@
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="13" t="str">
+      <c r="A34" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46276</v>
+      </c>
+      <c r="C34" s="8">
+        <v>46277</v>
+      </c>
+      <c r="D34" s="9">
+        <v>180</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>350</v>
+      </c>
+      <c r="G34" s="9">
+        <v>7</v>
+      </c>
+      <c r="H34" s="9">
+        <v>180</v>
+      </c>
+      <c r="I34" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="13" t="str">
+        <v>93263</v>
+      </c>
+      <c r="J34" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="16"/>
+        <v>-91823</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="13" t="str">
+      <c r="A35" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46277</v>
+      </c>
+      <c r="C35" s="8">
+        <v>46278</v>
+      </c>
+      <c r="D35" s="9">
+        <v>120</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <v>300</v>
+      </c>
+      <c r="G35" s="9">
+        <v>6</v>
+      </c>
+      <c r="H35" s="9">
+        <v>180</v>
+      </c>
+      <c r="I35" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="13" t="str">
+        <v>93155</v>
+      </c>
+      <c r="J35" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="16"/>
+        <v>-91715</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="8"/>
